--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q100_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03312877418224675</v>
+        <v>0.01642906623936264</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03312877418224675</v>
+        <v>0.01642906623936264</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.07076484604910595</v>
+        <v>0.03583986946440011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07076484604910595</v>
+        <v>0.03583986946440011</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1358952129450819</v>
+        <v>0.06843658076108054</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1358952129450819</v>
+        <v>0.06843658076108054</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2001986258067172</v>
+        <v>0.1010902283623038</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2001986258067172</v>
+        <v>0.1010902283623038</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2179205108393912</v>
+        <v>0.109965358031003</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2179205108393912</v>
+        <v>0.109965358031003</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2040632720844437</v>
+        <v>0.1029575870817139</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2040632720844437</v>
+        <v>0.1029575870817139</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1907785947991077</v>
+        <v>0.09627534949673071</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1907785947991077</v>
+        <v>0.09627534949673071</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1826413368707714</v>
+        <v>0.09233195556166815</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1826413368707714</v>
+        <v>0.09233195556166815</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
